--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Permessi per sosta e circolazione.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Permessi per sosta e circolazione.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="144">
   <si>
     <r>
       <t xml:space="preserve">
@@ -179,7 +179,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Richiedi permesso</t>
+    <t>Richiedi un permesso</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -348,7 +348,37 @@
     </r>
   </si>
   <si>
-    <t/>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>Richiesta di integrazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>La tua richiesta è stata accolta</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>La tua richiesta non è stata accolta</t>
+    </r>
   </si>
   <si>
     <r>
@@ -414,17 +444,6 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t>Il tuo contrassegno sta per scadere</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>La tua richiesta è stata accolta</t>
     </r>
   </si>
   <si>
@@ -915,7 +934,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -995,7 +1014,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -1403,7 +1422,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1516,28 +1535,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firma con IO
-Tramite la funzionalità Firma con IO puoi inviare al destinatario il documento da firmare e permettere la firma direttamente in app. Scopri di più (https://firma.io.italia.it/)
-Il seguente messaggio è da utilizzare nei casi di altre modalità di firma e non è necessario quando si utilizza Firma con IO.
-✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -2279,154 +2276,154 @@
         <v>83</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G4" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="M4" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="33" t="s">
+      <c r="N4" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="O4" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="K4" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="M4" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="N4" s="33" t="s">
+      <c r="P4" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="P4" s="33" t="s">
-        <v>90</v>
-      </c>
       <c r="Q4" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H5" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="N5" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="O5" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="L5" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="M5" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="N5" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="O5" s="34" t="s">
-        <v>99</v>
-      </c>
       <c r="P5" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q5" s="34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>108</v>
-      </c>
       <c r="F6" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J6" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="N6" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="L6" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>111</v>
-      </c>
       <c r="O6" s="34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q6" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>64</v>
@@ -2479,172 +2476,172 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F9" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>121</v>
-      </c>
       <c r="J9" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F10" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="M10" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="H10" s="34" t="s">
+      <c r="N10" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="I10" s="34" t="s">
+      <c r="O10" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="J10" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="M10" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="O10" s="34" t="s">
-        <v>137</v>
-      </c>
       <c r="P10" s="34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>64</v>
@@ -2656,16 +2653,16 @@
         <v>64</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="K11" s="34" t="s">
         <v>64</v>
@@ -2677,10 +2674,10 @@
         <v>64</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>64</v>
